--- a/sample-document/01_Commercial_Invoice.xlsx
+++ b/sample-document/01_Commercial_Invoice.xlsx
@@ -479,7 +479,6 @@
           <t>Saigon Textile Export Co., Ltd.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Invoice No:</t>
@@ -490,7 +489,6 @@
           <t>INV-2026-0418</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
@@ -499,7 +497,6 @@
           <t>123 Nguyen Hue Blvd, District 1, Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Invoice Date:</t>
@@ -510,7 +507,6 @@
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -523,7 +519,6 @@
           <t>Tokyo Apparel Import K.K.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>P/O No:</t>
@@ -534,7 +529,6 @@
           <t>PO-TA-26-0331</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr"/>
@@ -543,7 +537,6 @@
           <t>4-5-6 Nihonbashi, Chuo-ku, Tokyo 103-0027, Japan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Payment:</t>
@@ -554,7 +547,6 @@
           <t>T/T 30 days after B/L date</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -567,7 +559,6 @@
           <t>OCEAN HARMONY V.025E</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Incoterms:</t>
@@ -575,10 +566,9 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CIF Tokyo</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>FOB Ho Chi Minh City</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -591,7 +581,6 @@
           <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>B/L No:</t>
@@ -602,7 +591,6 @@
           <t>SGNTYO260418</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -615,7 +603,6 @@
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Country of Origin:</t>
@@ -626,7 +613,6 @@
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
